--- a/data/trans_orig/P1412-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1412-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de angina de pecho en 2012</t>
+          <t>Población con diagnóstico de angina de pecho en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,97 +732,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2091</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2072</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8189</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2091</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7435</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6386</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2091</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>7381</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>435139</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>437211</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>307019</t>
+          <t>306265</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>744284</t>
+          <t>745279</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5838</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,62 +1110,62 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1032</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2120</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>5197</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1032</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>5938</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>412959</t>
+          <t>413013</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>335891</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>338011</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>750870</t>
+          <t>751611</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15023</t>
+          <t>13720</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15722</t>
+          <t>14767</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>614392</t>
+          <t>615695</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>628066</t>
+          <t>627527</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>258091</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>260129</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>873822</t>
+          <t>874777</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>887694</t>
+          <t>888444</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,88%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20444</t>
+          <t>20220</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>5552</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7150</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21523</t>
+          <t>22547</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1138565</t>
+          <t>1138789</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1152771</t>
+          <t>1152903</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>758224</t>
+          <t>758223</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1901261</t>
+          <t>1900237</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1915634</t>
+          <t>1915149</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10725</t>
+          <t>11736</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5418</t>
+          <t>5516</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19164</t>
+          <t>19033</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9480</t>
+          <t>8587</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25900</t>
+          <t>24239</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>499871</t>
+          <t>498860</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>741082</t>
+          <t>741213</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>754828</t>
+          <t>754730</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1244943</t>
+          <t>1246604</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1261363</t>
+          <t>1262256</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19723</t>
+          <t>19425</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5426</t>
+          <t>5362</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19684</t>
+          <t>19639</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264956</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266882</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1088446</t>
+          <t>1088744</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1102634</t>
+          <t>1102824</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1355367</t>
+          <t>1355412</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1369625</t>
+          <t>1369689</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14227</t>
+          <t>14954</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35141</t>
+          <t>35033</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15765</t>
+          <t>16596</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35870</t>
+          <t>36019</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33345</t>
+          <t>35826</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63079</t>
+          <t>64291</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3386769</t>
+          <t>3386877</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3407683</t>
+          <t>3406956</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3508915</t>
+          <t>3508766</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3529020</t>
+          <t>3528189</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6903615</t>
+          <t>6902403</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6933349</t>
+          <t>6930868</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de angina de pecho en 2016</t>
+          <t>Población con diagnóstico de angina de pecho en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>928</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11307</t>
+          <t>11651</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10835</t>
+          <t>12558</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417785</t>
+          <t>417441</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>428174</t>
+          <t>428164</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>345054</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>347055</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>765312</t>
+          <t>763589</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3710,97 +3710,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2040</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>2036</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>375187</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>377227</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>370249</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>372273</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>747464</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>749500</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>862</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8033</t>
+          <t>7889</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>863</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8184</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>513881</t>
+          <t>514025</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>521056</t>
+          <t>521052</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>164054</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166123</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>679852</t>
+          <t>680038</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>687175</t>
+          <t>687173</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6292</t>
+          <t>6539</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20869</t>
+          <t>20502</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7623</t>
+          <t>7613</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8195</t>
+          <t>7942</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23168</t>
+          <t>23318</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1128769</t>
+          <t>1129136</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1143346</t>
+          <t>1143099</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>818253</t>
+          <t>818263</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1952346</t>
+          <t>1952196</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1967319</t>
+          <t>1967572</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3199</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14022</t>
+          <t>13480</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,82 +4754,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>5617</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2123</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>12730</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>13087</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>7069</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>21347</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>0,52%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>5617</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>12190</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>13087</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>7103</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>21842</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>606684</t>
+          <t>607226</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>617507</t>
+          <t>617552</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>726054</t>
+          <t>725514</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>736112</t>
+          <t>736121</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1337108</t>
+          <t>1337603</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1351847</t>
+          <t>1351881</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5520</t>
+          <t>5526</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20420</t>
+          <t>19990</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5566</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19836</t>
+          <t>19651</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>285126</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287145</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1061605</t>
+          <t>1062035</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1076505</t>
+          <t>1076499</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1349334</t>
+          <t>1349519</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1363604</t>
+          <t>1363640</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17245</t>
+          <t>16936</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38189</t>
+          <t>38355</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30485</t>
+          <t>31032</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33012</t>
+          <t>33239</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>60828</t>
+          <t>60714</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3347533</t>
+          <t>3347367</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3368477</t>
+          <t>3368786</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3501111</t>
+          <t>3500564</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6856490</t>
+          <t>6856604</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6884306</t>
+          <t>6884079</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5807,7 +5807,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de angina de pecho en 2023</t>
+          <t>Población con diagnóstico de angina de pecho en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>3298</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13179</t>
+          <t>13128</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6857</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5333</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16294</t>
+          <t>16771</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>492033</t>
+          <t>492084</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>502074</t>
+          <t>501914</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>440610</t>
+          <t>441044</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>446270</t>
+          <t>446349</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>936385</t>
+          <t>935908</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>947346</t>
+          <t>947591</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>556</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>828</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8088</t>
+          <t>7652</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>446201</t>
+          <t>445153</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>451643</t>
+          <t>451657</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>378334</t>
+          <t>378559</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>825349</t>
+          <t>825785</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>832450</t>
+          <t>832609</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,9%</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>12573</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6703,82 +6703,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3067</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>6211</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>1691</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>12079</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>512</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2714</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>6211</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>1543</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>12559</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>655129</t>
+          <t>654972</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>666195</t>
+          <t>666305</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6816,82 +6816,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>99,81%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>166399</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>163844</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>166911</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>99,69%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>98,16%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>766</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>828245</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>822377</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>832765</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>99,26%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>98,55%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>99,8%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>166399</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>164197</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>166911</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,69%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>98,37%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>766</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>828245</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>821897</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>832913</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>98,49%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>6468</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18706</t>
+          <t>19481</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>8844</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8982</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23678</t>
+          <t>25072</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1014755</t>
+          <t>1013980</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1027056</t>
+          <t>1026993</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>968396</t>
+          <t>968519</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>975802</t>
+          <t>975783</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1987146</t>
+          <t>1985752</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2001842</t>
+          <t>2001652</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1597</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7847</t>
+          <t>7632</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7527</t>
+          <t>7226</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13080</t>
+          <t>12799</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>464880</t>
+          <t>465095</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>471130</t>
+          <t>471333</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>831309</t>
+          <t>831610</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>836845</t>
+          <t>836842</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1298483</t>
+          <t>1298764</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1307061</t>
+          <t>1307361</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2426</t>
+          <t>2253</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9046</t>
+          <t>9128</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2249</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8971</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236427</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>751248</t>
+          <t>751166</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>757868</t>
+          <t>758041</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>991830</t>
+          <t>991917</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>998320</t>
+          <t>998552</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20648</t>
+          <t>21211</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40535</t>
+          <t>41283</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11848</t>
+          <t>11772</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24944</t>
+          <t>24812</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35074</t>
+          <t>35465</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>59715</t>
+          <t>59257</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3331130</t>
+          <t>3330382</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3351017</t>
+          <t>3350454</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3547151</t>
+          <t>3547283</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3560247</t>
+          <t>3560323</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6884045</t>
+          <t>6884503</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6908686</t>
+          <t>6908295</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">

--- a/data/trans_orig/P1412-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1412-Clase-trans_orig.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6386</t>
+          <t>8303</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>306265</t>
+          <t>307019</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>745279</t>
+          <t>743362</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5784</t>
+          <t>5881</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5197</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>413013</t>
+          <t>412916</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>751611</t>
+          <t>751598</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13720</t>
+          <t>15312</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14767</t>
+          <t>14547</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>615695</t>
+          <t>614103</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>627527</t>
+          <t>627434</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>874777</t>
+          <t>874997</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>888444</t>
+          <t>887590</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>6949</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20220</t>
+          <t>22183</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>6551</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22547</t>
+          <t>22073</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1138789</t>
+          <t>1136826</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1152903</t>
+          <t>1152060</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>758223</t>
+          <t>758744</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1900237</t>
+          <t>1900711</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1915149</t>
+          <t>1916233</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11736</t>
+          <t>9953</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5516</t>
+          <t>5499</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19033</t>
+          <t>18814</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8587</t>
+          <t>8022</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24239</t>
+          <t>24575</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>498860</t>
+          <t>500643</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>741213</t>
+          <t>741432</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>754730</t>
+          <t>754747</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1246604</t>
+          <t>1246268</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1262256</t>
+          <t>1262821</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19425</t>
+          <t>18978</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19639</t>
+          <t>19404</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1088744</t>
+          <t>1089191</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1102824</t>
+          <t>1102900</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1355412</t>
+          <t>1355647</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1369689</t>
+          <t>1369716</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14954</t>
+          <t>14513</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35033</t>
+          <t>35481</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,47 +2805,47 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>24778</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>15745</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>37905</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
           <t>0,44%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>24778</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>16596</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>36019</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35826</t>
+          <t>34163</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>64291</t>
+          <t>62861</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3386877</t>
+          <t>3386429</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3406956</t>
+          <t>3407397</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,49 +2918,49 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>99,58%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>3263</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>3520007</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>3506880</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3529040</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>99,3%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>98,93%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
           <t>99,56%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>3263</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>3520007</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>3508766</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>3528189</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,3%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>98,98%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,53%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>6447</t>
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6902403</t>
+          <t>6903833</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6930868</t>
+          <t>6932531</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>927</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11651</t>
+          <t>10685</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>921</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12558</t>
+          <t>11034</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417441</t>
+          <t>418407</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>428164</t>
+          <t>428165</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>763589</t>
+          <t>765113</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>775217</t>
+          <t>775226</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>856</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7889</t>
+          <t>8716</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>7979</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>514025</t>
+          <t>513198</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>521052</t>
+          <t>521058</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>680038</t>
+          <t>680057</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6539</t>
+          <t>6612</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20502</t>
+          <t>20322</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7613</t>
+          <t>7625</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7942</t>
+          <t>7910</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23318</t>
+          <t>23012</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1129136</t>
+          <t>1129316</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1143099</t>
+          <t>1143026</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>818263</t>
+          <t>818251</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1952196</t>
+          <t>1952502</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1967572</t>
+          <t>1967604</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>3552</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13480</t>
+          <t>14820</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2123</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12730</t>
+          <t>12777</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21347</t>
+          <t>21854</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>607226</t>
+          <t>605886</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>617552</t>
+          <t>617154</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>725514</t>
+          <t>725467</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>736121</t>
+          <t>736109</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1337603</t>
+          <t>1337096</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1351881</t>
+          <t>1351728</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5526</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19990</t>
+          <t>19527</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5530</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19651</t>
+          <t>18826</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1062035</t>
+          <t>1062498</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1076499</t>
+          <t>1076520</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1349519</t>
+          <t>1350344</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1363640</t>
+          <t>1363770</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16936</t>
+          <t>17441</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38355</t>
+          <t>37390</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11335</t>
+          <t>11357</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31032</t>
+          <t>30590</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33239</t>
+          <t>32977</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>60714</t>
+          <t>59191</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3347367</t>
+          <t>3348332</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3368786</t>
+          <t>3368281</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3500564</t>
+          <t>3501006</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3520261</t>
+          <t>3520239</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6856604</t>
+          <t>6858127</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6884079</t>
+          <t>6884341</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -5997,17 +5997,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>7123</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>3239</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13128</t>
+          <t>13416</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6032,32 +6032,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3087</t>
+          <t>3407</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6423</t>
+          <t>7288</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6067,17 +6067,17 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9606</t>
+          <t>10530</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5088</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16771</t>
+          <t>17213</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -6110,17 +6110,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>498694</t>
+          <t>543495</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>492084</t>
+          <t>537202</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>501914</t>
+          <t>547379</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6145,32 +6145,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>444380</t>
+          <t>485004</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>441044</t>
+          <t>481123</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>446349</t>
+          <t>487114</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6180,17 +6180,17 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>943073</t>
+          <t>1028499</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>935908</t>
+          <t>1021816</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>947591</t>
+          <t>1032950</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -6223,17 +6223,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6258,17 +6258,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6293,17 +6293,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6340,22 +6340,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>587</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>7392</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>562</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>2813</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6410,32 +6410,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2962</t>
+          <t>3150</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>593</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7652</t>
+          <t>8531</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -6453,27 +6453,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>449815</t>
+          <t>480624</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>445153</t>
+          <t>475820</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>451657</t>
+          <t>482625</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6488,27 +6488,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>380661</t>
+          <t>421219</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>378559</t>
+          <t>418968</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>381225</t>
+          <t>421781</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,87%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6523,32 +6523,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>830475</t>
+          <t>901843</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>825785</t>
+          <t>896462</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>832609</t>
+          <t>904400</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,93%</t>
         </is>
       </c>
     </row>
@@ -6566,17 +6566,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6601,17 +6601,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381225</t>
+          <t>421781</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381225</t>
+          <t>421781</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>381225</t>
+          <t>421781</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6636,17 +6636,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>833437</t>
+          <t>904993</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>833437</t>
+          <t>904993</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>833437</t>
+          <t>904993</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6683,32 +6683,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>6464</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>3031</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12573</t>
+          <t>11910</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>554</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -6728,12 +6728,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6753,32 +6753,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6211</t>
+          <t>7017</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1691</t>
+          <t>3696</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12079</t>
+          <t>13098</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -6796,32 +6796,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>661846</t>
+          <t>464279</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>654972</t>
+          <t>458833</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>666305</t>
+          <t>467712</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6831,27 +6831,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>166399</t>
+          <t>186943</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>163844</t>
+          <t>184642</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6866,32 +6866,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>828245</t>
+          <t>651224</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>822377</t>
+          <t>645143</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>832765</t>
+          <t>654545</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -6909,17 +6909,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6944,17 +6944,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6979,17 +6979,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7026,32 +7026,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11239</t>
+          <t>11982</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6468</t>
+          <t>6797</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19481</t>
+          <t>20329</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7061,32 +7061,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4293</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>2384</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8844</t>
+          <t>9891</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7096,32 +7096,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>15531</t>
+          <t>17132</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9172</t>
+          <t>10918</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25072</t>
+          <t>25587</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -7139,32 +7139,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1022222</t>
+          <t>1118505</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1013980</t>
+          <t>1110158</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1026993</t>
+          <t>1123690</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7174,32 +7174,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>973070</t>
+          <t>855340</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>968519</t>
+          <t>850598</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>975783</t>
+          <t>858105</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7209,32 +7209,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1995293</t>
+          <t>1973844</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1985752</t>
+          <t>1965389</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2001652</t>
+          <t>1980058</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -7252,17 +7252,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1033461</t>
+          <t>1130487</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1033461</t>
+          <t>1130487</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1033461</t>
+          <t>1130487</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7287,17 +7287,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977363</t>
+          <t>860489</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977363</t>
+          <t>860489</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977363</t>
+          <t>860489</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7322,17 +7322,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2010824</t>
+          <t>1990976</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2010824</t>
+          <t>1990976</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2010824</t>
+          <t>1990976</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7369,32 +7369,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>3718</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7632</t>
+          <t>8253</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7404,32 +7404,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>5019</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7226</t>
+          <t>8901</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7439,32 +7439,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>7599</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4202</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12799</t>
+          <t>13594</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -7482,32 +7482,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>469141</t>
+          <t>561860</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>465095</t>
+          <t>557325</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>471333</t>
+          <t>564135</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7517,32 +7517,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>834824</t>
+          <t>824400</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>831610</t>
+          <t>820518</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>836842</t>
+          <t>826884</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7552,32 +7552,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1303964</t>
+          <t>1386260</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1298764</t>
+          <t>1381403</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1307361</t>
+          <t>1389882</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -7595,17 +7595,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>472727</t>
+          <t>565578</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>472727</t>
+          <t>565578</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>472727</t>
+          <t>565578</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7630,17 +7630,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838836</t>
+          <t>829419</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838836</t>
+          <t>829419</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838836</t>
+          <t>829419</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7665,17 +7665,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1311563</t>
+          <t>1394997</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1311563</t>
+          <t>1394997</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1311563</t>
+          <t>1394997</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7697,7 +7697,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7747,32 +7747,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4817</t>
+          <t>5589</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2253</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9128</t>
+          <t>10684</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7782,32 +7782,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>4817</t>
+          <t>5589</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2249</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>10441</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -7825,7 +7825,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -7860,32 +7860,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>755477</t>
+          <t>837606</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>751166</t>
+          <t>832511</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>758041</t>
+          <t>840452</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7895,32 +7895,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>995984</t>
+          <t>1074834</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>991917</t>
+          <t>1069982</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>998552</t>
+          <t>1077603</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -7938,17 +7938,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7973,17 +7973,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760294</t>
+          <t>843195</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760294</t>
+          <t>843195</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760294</t>
+          <t>843195</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8008,17 +8008,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000801</t>
+          <t>1080423</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000801</t>
+          <t>1080423</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000801</t>
+          <t>1080423</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8055,32 +8055,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>29440</t>
+          <t>31874</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21211</t>
+          <t>22594</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41283</t>
+          <t>42718</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8090,32 +8090,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>17285</t>
+          <t>20281</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11772</t>
+          <t>14621</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24812</t>
+          <t>28233</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8125,32 +8125,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>46726</t>
+          <t>52155</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35465</t>
+          <t>41471</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>59257</t>
+          <t>65960</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -8168,32 +8168,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3342225</t>
+          <t>3405992</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3330382</t>
+          <t>3395148</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3350454</t>
+          <t>3415272</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8203,32 +8203,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3554810</t>
+          <t>3610511</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3547283</t>
+          <t>3602559</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3560323</t>
+          <t>3616171</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8238,32 +8238,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6897034</t>
+          <t>7016504</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6884503</t>
+          <t>7002699</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6908295</t>
+          <t>7027188</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -8281,17 +8281,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3371665</t>
+          <t>3437866</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3371665</t>
+          <t>3437866</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3371665</t>
+          <t>3437866</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8316,17 +8316,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3572095</t>
+          <t>3630792</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3572095</t>
+          <t>3630792</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3572095</t>
+          <t>3630792</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8351,17 +8351,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6943760</t>
+          <t>7068659</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6943760</t>
+          <t>7068659</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6943760</t>
+          <t>7068659</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
